--- a/data/review/crosscheck_B.xlsx
+++ b/data/review/crosscheck_B.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Gán nhãn" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gán nhãn'!$A$1:$R$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gán nhãn'!$A$1:$S$301</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn phiên bản 1.2 · 300 dòng · bản đầy đủ: docs/vilextime-annotation.md</t>
+          <t>Hướng dẫn phiên bản 2.0 · 300 dòng · bản đầy đủ: docs/vilextime-annotation.md</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>T2   Cặp tương phản. Hai dòng cùng lineage, hai mốc. Kiểm xem đáp án hai mốc có THẬT SỰ khác nhau ở chỗ câu hỏi chạm tới. Giống nhau thì group_mismatch.</t>
+          <t>T2   Cặp tương phản (gồm cả cặp gần giống). Hai dòng cùng lineage, hai mốc. Luật sư trả lời giống nhau ở cả hai ngày thì group_mismatch, kể cả khi chỉ đổi cách viết cùng một điều. Câu hỏi chứa sẵn vế trước của đáp án: dòng ngày trước question_leaks. Đổi chủ thể giữa hai mốc: dòng ngày sau gold_wrong, ghi note.</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>T6   Hết hiệu lực một phần ở cấp Khoản/Điểm. Đáp án đúng thường là "không còn hiệu lực" kèm lý do, nên cột đáp án ghi "(không có đáp án: ...)". Câu hỏi không được là dạng có/không.</t>
+          <t>T6   Hết hiệu lực một phần ở cấp Khoản/Điểm. Cột đáp án ghi "(không có đáp án: ...)". Câu hỏi không được là dạng có/không. Nếu nội dung đã CHUYỂN CHỖ (đạt đủ 7 yếu tố, hướng dẫn §3) thì đáp án rỗng là sai: khong_dat, gold_wrong, ghi chỗ mới vào note. Không chắc thì vẫn dat (nếu không có lỗi khác) và ghi "unclear" vào note.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Ngưỡng của khóa luận là κ ≥ 0,6. Thấp hơn thì viết lại hướng dẫn và kiểm lại,</t>
+          <t>Ngưỡng đăng ký trước là AC1 ≥ 0,80 và p_neg ≥ 0,60. Thấp hơn thì viết lại hướng dẫn và kiểm lại,</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Cột đáp án không đúng là điều khoản có hiệu lực tại as_of: sai phiên bản, vế "trước sửa đổi" thực ra đã là bản sửa, hoặc text bị cắt mất phần được hỏi.</t>
+          <t>Cột đáp án không đúng là điều khoản có hiệu lực tại as_of: sai phiên bản, vế "trước sửa đổi" thực ra đã là bản sửa, text bị cắt mất phần được hỏi, hoặc (T6) đáp án rỗng trong khi nội dung đã chuyển chỗ.</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Điều khoản chuyển tiếp của văn bản sửa đổi giữ quy định cũ cho đúng quan hệ trong câu hỏi, nên cột đáp án không phải quy định được áp dụng. Ghi Điều chuyển tiếp vào note.</t>
+          <t>Điều khoản chuyển tiếp giữ quy định cũ cho đúng quan hệ câu hỏi tự nêu (ví dụ hồ sơ nộp trước ngày hiệu lực), hoặc cho chính sự việc phát sinh tại as_of. Câu hỏi không nêu gì thì hiểu sự việc phát sinh tại as_of: điều khoản chỉ giữ bản cũ cho việc đang thực hiện KHÔNG phải lỗi. Ghi Điều chuyển tiếp vào note.</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R301"/>
+  <dimension ref="A1:S301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1010,6 +1010,7 @@
     <col width="26" customWidth="1" min="16" max="16"/>
     <col width="34" customWidth="1" min="17" max="17"/>
     <col width="46" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1103,6 +1104,11 @@
           <t>suggestion</t>
         </is>
       </c>
+      <c r="S1" s="10" t="inlineStr">
+        <is>
+          <t>guideline_version</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
@@ -1175,6 +1181,11 @@
       <c r="P2" s="8" t="inlineStr"/>
       <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -1239,6 +1250,11 @@
       <c r="P3" s="8" t="inlineStr"/>
       <c r="Q3" s="8" t="inlineStr"/>
       <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -1319,6 +1335,11 @@
         </is>
       </c>
       <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -1391,6 +1412,11 @@
         </is>
       </c>
       <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -1459,6 +1485,7 @@
       <c r="P6" s="15" t="inlineStr"/>
       <c r="Q6" s="15" t="inlineStr"/>
       <c r="R6" s="15" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -1515,6 +1542,7 @@
       <c r="P7" s="15" t="inlineStr"/>
       <c r="Q7" s="15" t="inlineStr"/>
       <c r="R7" s="15" t="inlineStr"/>
+      <c r="S7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -1583,6 +1611,7 @@
       <c r="P8" s="15" t="inlineStr"/>
       <c r="Q8" s="15" t="inlineStr"/>
       <c r="R8" s="15" t="inlineStr"/>
+      <c r="S8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -1639,6 +1668,7 @@
       <c r="P9" s="15" t="inlineStr"/>
       <c r="Q9" s="15" t="inlineStr"/>
       <c r="R9" s="15" t="inlineStr"/>
+      <c r="S9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -1707,6 +1737,7 @@
       <c r="P10" s="15" t="inlineStr"/>
       <c r="Q10" s="15" t="inlineStr"/>
       <c r="R10" s="15" t="inlineStr"/>
+      <c r="S10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -1767,6 +1798,7 @@
       <c r="P11" s="15" t="inlineStr"/>
       <c r="Q11" s="15" t="inlineStr"/>
       <c r="R11" s="15" t="inlineStr"/>
+      <c r="S11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -1847,6 +1879,11 @@
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
       <c r="R12" s="8" t="inlineStr"/>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -1923,6 +1960,11 @@
       <c r="P13" s="8" t="inlineStr"/>
       <c r="Q13" s="8" t="inlineStr"/>
       <c r="R13" s="8" t="inlineStr"/>
+      <c r="S13" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -1991,6 +2033,7 @@
       <c r="P14" s="15" t="inlineStr"/>
       <c r="Q14" s="15" t="inlineStr"/>
       <c r="R14" s="15" t="inlineStr"/>
+      <c r="S14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -2047,6 +2090,7 @@
       <c r="P15" s="15" t="inlineStr"/>
       <c r="Q15" s="15" t="inlineStr"/>
       <c r="R15" s="15" t="inlineStr"/>
+      <c r="S15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -2119,6 +2163,7 @@
       <c r="P16" s="15" t="inlineStr"/>
       <c r="Q16" s="15" t="inlineStr"/>
       <c r="R16" s="15" t="inlineStr"/>
+      <c r="S16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -2187,6 +2232,7 @@
       <c r="P17" s="15" t="inlineStr"/>
       <c r="Q17" s="15" t="inlineStr"/>
       <c r="R17" s="15" t="inlineStr"/>
+      <c r="S17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -2267,6 +2313,11 @@
       <c r="P18" s="8" t="inlineStr"/>
       <c r="Q18" s="8" t="inlineStr"/>
       <c r="R18" s="8" t="inlineStr"/>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -2343,6 +2394,11 @@
       <c r="P19" s="8" t="inlineStr"/>
       <c r="Q19" s="8" t="inlineStr"/>
       <c r="R19" s="8" t="inlineStr"/>
+      <c r="S19" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -2423,6 +2479,11 @@
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr"/>
+      <c r="S20" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -2491,6 +2552,11 @@
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr"/>
+      <c r="S21" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -2563,6 +2629,11 @@
       <c r="P22" s="8" t="inlineStr"/>
       <c r="Q22" s="8" t="inlineStr"/>
       <c r="R22" s="8" t="inlineStr"/>
+      <c r="S22" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -2639,6 +2710,11 @@
       <c r="P23" s="8" t="inlineStr"/>
       <c r="Q23" s="8" t="inlineStr"/>
       <c r="R23" s="8" t="inlineStr"/>
+      <c r="S23" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -2711,6 +2787,11 @@
       <c r="P24" s="8" t="inlineStr"/>
       <c r="Q24" s="8" t="inlineStr"/>
       <c r="R24" s="8" t="inlineStr"/>
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -2783,6 +2864,7 @@
       <c r="P25" s="15" t="inlineStr"/>
       <c r="Q25" s="15" t="inlineStr"/>
       <c r="R25" s="15" t="inlineStr"/>
+      <c r="S25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -2855,6 +2937,7 @@
       <c r="P26" s="15" t="inlineStr"/>
       <c r="Q26" s="15" t="inlineStr"/>
       <c r="R26" s="15" t="inlineStr"/>
+      <c r="S26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -2935,6 +3018,11 @@
       <c r="P27" s="8" t="inlineStr"/>
       <c r="Q27" s="8" t="inlineStr"/>
       <c r="R27" s="8" t="inlineStr"/>
+      <c r="S27" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -3011,6 +3099,11 @@
       <c r="P28" s="8" t="inlineStr"/>
       <c r="Q28" s="8" t="inlineStr"/>
       <c r="R28" s="8" t="inlineStr"/>
+      <c r="S28" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -3083,6 +3176,7 @@
       <c r="P29" s="15" t="inlineStr"/>
       <c r="Q29" s="15" t="inlineStr"/>
       <c r="R29" s="15" t="inlineStr"/>
+      <c r="S29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -3151,6 +3245,7 @@
       <c r="P30" s="15" t="inlineStr"/>
       <c r="Q30" s="15" t="inlineStr"/>
       <c r="R30" s="15" t="inlineStr"/>
+      <c r="S30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -3219,6 +3314,7 @@
       <c r="P31" s="15" t="inlineStr"/>
       <c r="Q31" s="15" t="inlineStr"/>
       <c r="R31" s="15" t="inlineStr"/>
+      <c r="S31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -3275,6 +3371,7 @@
       <c r="P32" s="15" t="inlineStr"/>
       <c r="Q32" s="15" t="inlineStr"/>
       <c r="R32" s="15" t="inlineStr"/>
+      <c r="S32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -3343,6 +3440,7 @@
       <c r="P33" s="15" t="inlineStr"/>
       <c r="Q33" s="15" t="inlineStr"/>
       <c r="R33" s="15" t="inlineStr"/>
+      <c r="S33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -3399,6 +3497,7 @@
       <c r="P34" s="15" t="inlineStr"/>
       <c r="Q34" s="15" t="inlineStr"/>
       <c r="R34" s="15" t="inlineStr"/>
+      <c r="S34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -3475,6 +3574,11 @@
       <c r="P35" s="8" t="inlineStr"/>
       <c r="Q35" s="8" t="inlineStr"/>
       <c r="R35" s="8" t="inlineStr"/>
+      <c r="S35" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -3551,6 +3655,11 @@
       <c r="P36" s="8" t="inlineStr"/>
       <c r="Q36" s="8" t="inlineStr"/>
       <c r="R36" s="8" t="inlineStr"/>
+      <c r="S36" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -3623,6 +3732,11 @@
       <c r="P37" s="8" t="inlineStr"/>
       <c r="Q37" s="8" t="inlineStr"/>
       <c r="R37" s="8" t="inlineStr"/>
+      <c r="S37" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -3699,6 +3813,11 @@
       <c r="P38" s="8" t="inlineStr"/>
       <c r="Q38" s="8" t="inlineStr"/>
       <c r="R38" s="8" t="inlineStr"/>
+      <c r="S38" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -3775,6 +3894,11 @@
       <c r="P39" s="8" t="inlineStr"/>
       <c r="Q39" s="8" t="inlineStr"/>
       <c r="R39" s="8" t="inlineStr"/>
+      <c r="S39" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -3851,6 +3975,11 @@
       <c r="P40" s="8" t="inlineStr"/>
       <c r="Q40" s="8" t="inlineStr"/>
       <c r="R40" s="8" t="inlineStr"/>
+      <c r="S40" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -3923,6 +4052,11 @@
       <c r="P41" s="8" t="inlineStr"/>
       <c r="Q41" s="8" t="inlineStr"/>
       <c r="R41" s="8" t="inlineStr"/>
+      <c r="S41" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -3987,6 +4121,11 @@
       <c r="P42" s="8" t="inlineStr"/>
       <c r="Q42" s="8" t="inlineStr"/>
       <c r="R42" s="8" t="inlineStr"/>
+      <c r="S42" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -4063,6 +4202,11 @@
       <c r="P43" s="8" t="inlineStr"/>
       <c r="Q43" s="8" t="inlineStr"/>
       <c r="R43" s="8" t="inlineStr"/>
+      <c r="S43" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -4147,6 +4291,11 @@
         </is>
       </c>
       <c r="R44" s="8" t="inlineStr"/>
+      <c r="S44" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -4227,6 +4376,11 @@
         </is>
       </c>
       <c r="R45" s="8" t="inlineStr"/>
+      <c r="S45" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -4303,6 +4457,11 @@
       <c r="P46" s="8" t="inlineStr"/>
       <c r="Q46" s="8" t="inlineStr"/>
       <c r="R46" s="8" t="inlineStr"/>
+      <c r="S46" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -4375,6 +4534,11 @@
       <c r="P47" s="8" t="inlineStr"/>
       <c r="Q47" s="8" t="inlineStr"/>
       <c r="R47" s="8" t="inlineStr"/>
+      <c r="S47" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -4443,6 +4607,7 @@
       <c r="P48" s="15" t="inlineStr"/>
       <c r="Q48" s="15" t="inlineStr"/>
       <c r="R48" s="15" t="inlineStr"/>
+      <c r="S48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -4499,6 +4664,7 @@
       <c r="P49" s="15" t="inlineStr"/>
       <c r="Q49" s="15" t="inlineStr"/>
       <c r="R49" s="15" t="inlineStr"/>
+      <c r="S49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -4567,6 +4733,7 @@
       <c r="P50" s="15" t="inlineStr"/>
       <c r="Q50" s="15" t="inlineStr"/>
       <c r="R50" s="15" t="inlineStr"/>
+      <c r="S50" s="12" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -4623,6 +4790,7 @@
       <c r="P51" s="15" t="inlineStr"/>
       <c r="Q51" s="15" t="inlineStr"/>
       <c r="R51" s="15" t="inlineStr"/>
+      <c r="S51" s="12" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -4691,6 +4859,7 @@
       <c r="P52" s="15" t="inlineStr"/>
       <c r="Q52" s="15" t="inlineStr"/>
       <c r="R52" s="15" t="inlineStr"/>
+      <c r="S52" s="12" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -4747,6 +4916,7 @@
       <c r="P53" s="15" t="inlineStr"/>
       <c r="Q53" s="15" t="inlineStr"/>
       <c r="R53" s="15" t="inlineStr"/>
+      <c r="S53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -4819,6 +4989,7 @@
       <c r="P54" s="15" t="inlineStr"/>
       <c r="Q54" s="15" t="inlineStr"/>
       <c r="R54" s="15" t="inlineStr"/>
+      <c r="S54" s="12" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -4887,6 +5058,7 @@
       <c r="P55" s="15" t="inlineStr"/>
       <c r="Q55" s="15" t="inlineStr"/>
       <c r="R55" s="15" t="inlineStr"/>
+      <c r="S55" s="12" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -4963,6 +5135,11 @@
       <c r="P56" s="8" t="inlineStr"/>
       <c r="Q56" s="8" t="inlineStr"/>
       <c r="R56" s="8" t="inlineStr"/>
+      <c r="S56" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -5039,6 +5216,11 @@
       <c r="P57" s="8" t="inlineStr"/>
       <c r="Q57" s="8" t="inlineStr"/>
       <c r="R57" s="8" t="inlineStr"/>
+      <c r="S57" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -5107,6 +5289,11 @@
       <c r="P58" s="8" t="inlineStr"/>
       <c r="Q58" s="8" t="inlineStr"/>
       <c r="R58" s="8" t="inlineStr"/>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -5175,6 +5362,7 @@
       <c r="P59" s="15" t="inlineStr"/>
       <c r="Q59" s="15" t="inlineStr"/>
       <c r="R59" s="15" t="inlineStr"/>
+      <c r="S59" s="12" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -5235,6 +5423,7 @@
       <c r="P60" s="15" t="inlineStr"/>
       <c r="Q60" s="15" t="inlineStr"/>
       <c r="R60" s="15" t="inlineStr"/>
+      <c r="S60" s="12" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -5307,6 +5496,11 @@
       <c r="P61" s="8" t="inlineStr"/>
       <c r="Q61" s="8" t="inlineStr"/>
       <c r="R61" s="8" t="inlineStr"/>
+      <c r="S61" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5367,6 +5561,11 @@
       <c r="P62" s="8" t="inlineStr"/>
       <c r="Q62" s="8" t="inlineStr"/>
       <c r="R62" s="8" t="inlineStr"/>
+      <c r="S62" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -5435,6 +5634,7 @@
       <c r="P63" s="15" t="inlineStr"/>
       <c r="Q63" s="15" t="inlineStr"/>
       <c r="R63" s="15" t="inlineStr"/>
+      <c r="S63" s="12" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -5491,6 +5691,7 @@
       <c r="P64" s="15" t="inlineStr"/>
       <c r="Q64" s="15" t="inlineStr"/>
       <c r="R64" s="15" t="inlineStr"/>
+      <c r="S64" s="12" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -5559,6 +5760,7 @@
       <c r="P65" s="15" t="inlineStr"/>
       <c r="Q65" s="15" t="inlineStr"/>
       <c r="R65" s="15" t="inlineStr"/>
+      <c r="S65" s="12" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -5615,6 +5817,7 @@
       <c r="P66" s="15" t="inlineStr"/>
       <c r="Q66" s="15" t="inlineStr"/>
       <c r="R66" s="15" t="inlineStr"/>
+      <c r="S66" s="12" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -5695,6 +5898,11 @@
         </is>
       </c>
       <c r="R67" s="8" t="inlineStr"/>
+      <c r="S67" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -5779,6 +5987,11 @@
         </is>
       </c>
       <c r="R68" s="8" t="inlineStr"/>
+      <c r="S68" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -5859,6 +6072,11 @@
         </is>
       </c>
       <c r="R69" s="8" t="inlineStr"/>
+      <c r="S69" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -5935,6 +6153,11 @@
       <c r="P70" s="8" t="inlineStr"/>
       <c r="Q70" s="8" t="inlineStr"/>
       <c r="R70" s="8" t="inlineStr"/>
+      <c r="S70" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -6007,6 +6230,11 @@
       <c r="P71" s="8" t="inlineStr"/>
       <c r="Q71" s="8" t="inlineStr"/>
       <c r="R71" s="8" t="inlineStr"/>
+      <c r="S71" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -6075,6 +6303,7 @@
       <c r="P72" s="15" t="inlineStr"/>
       <c r="Q72" s="15" t="inlineStr"/>
       <c r="R72" s="15" t="inlineStr"/>
+      <c r="S72" s="12" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -6135,6 +6364,7 @@
       <c r="P73" s="15" t="inlineStr"/>
       <c r="Q73" s="15" t="inlineStr"/>
       <c r="R73" s="15" t="inlineStr"/>
+      <c r="S73" s="12" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -6203,6 +6433,7 @@
       <c r="P74" s="15" t="inlineStr"/>
       <c r="Q74" s="15" t="inlineStr"/>
       <c r="R74" s="15" t="inlineStr"/>
+      <c r="S74" s="12" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -6259,6 +6490,7 @@
       <c r="P75" s="15" t="inlineStr"/>
       <c r="Q75" s="15" t="inlineStr"/>
       <c r="R75" s="15" t="inlineStr"/>
+      <c r="S75" s="12" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -6339,6 +6571,11 @@
       <c r="P76" s="8" t="inlineStr"/>
       <c r="Q76" s="8" t="inlineStr"/>
       <c r="R76" s="8" t="inlineStr"/>
+      <c r="S76" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -6415,6 +6652,11 @@
       <c r="P77" s="8" t="inlineStr"/>
       <c r="Q77" s="8" t="inlineStr"/>
       <c r="R77" s="8" t="inlineStr"/>
+      <c r="S77" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -6495,6 +6737,11 @@
         </is>
       </c>
       <c r="R78" s="8" t="inlineStr"/>
+      <c r="S78" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -6579,6 +6826,11 @@
         </is>
       </c>
       <c r="R79" s="8" t="inlineStr"/>
+      <c r="S79" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -6659,6 +6911,11 @@
       <c r="P80" s="8" t="inlineStr"/>
       <c r="Q80" s="8" t="inlineStr"/>
       <c r="R80" s="8" t="inlineStr"/>
+      <c r="S80" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -6739,6 +6996,11 @@
       <c r="P81" s="8" t="inlineStr"/>
       <c r="Q81" s="8" t="inlineStr"/>
       <c r="R81" s="8" t="inlineStr"/>
+      <c r="S81" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -6819,6 +7081,11 @@
         </is>
       </c>
       <c r="R82" s="8" t="inlineStr"/>
+      <c r="S82" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -6887,6 +7154,11 @@
         </is>
       </c>
       <c r="R83" s="8" t="inlineStr"/>
+      <c r="S83" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
@@ -6963,6 +7235,11 @@
       <c r="P84" s="8" t="inlineStr"/>
       <c r="Q84" s="8" t="inlineStr"/>
       <c r="R84" s="8" t="inlineStr"/>
+      <c r="S84" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
@@ -7035,6 +7312,7 @@
       <c r="P85" s="15" t="inlineStr"/>
       <c r="Q85" s="15" t="inlineStr"/>
       <c r="R85" s="15" t="inlineStr"/>
+      <c r="S85" s="12" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
@@ -7119,6 +7397,11 @@
         </is>
       </c>
       <c r="R86" s="8" t="inlineStr"/>
+      <c r="S86" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
@@ -7203,6 +7486,11 @@
         </is>
       </c>
       <c r="R87" s="8" t="inlineStr"/>
+      <c r="S87" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -7283,6 +7571,11 @@
         </is>
       </c>
       <c r="R88" s="8" t="inlineStr"/>
+      <c r="S88" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -7355,6 +7648,7 @@
       <c r="P89" s="15" t="inlineStr"/>
       <c r="Q89" s="15" t="inlineStr"/>
       <c r="R89" s="15" t="inlineStr"/>
+      <c r="S89" s="12" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
@@ -7427,6 +7721,7 @@
       <c r="P90" s="15" t="inlineStr"/>
       <c r="Q90" s="15" t="inlineStr"/>
       <c r="R90" s="15" t="inlineStr"/>
+      <c r="S90" s="12" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -7495,6 +7790,7 @@
       <c r="P91" s="15" t="inlineStr"/>
       <c r="Q91" s="15" t="inlineStr"/>
       <c r="R91" s="15" t="inlineStr"/>
+      <c r="S91" s="12" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -7551,6 +7847,7 @@
       <c r="P92" s="15" t="inlineStr"/>
       <c r="Q92" s="15" t="inlineStr"/>
       <c r="R92" s="15" t="inlineStr"/>
+      <c r="S92" s="12" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
@@ -7619,6 +7916,7 @@
       <c r="P93" s="15" t="inlineStr"/>
       <c r="Q93" s="15" t="inlineStr"/>
       <c r="R93" s="15" t="inlineStr"/>
+      <c r="S93" s="12" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
@@ -7675,6 +7973,7 @@
       <c r="P94" s="15" t="inlineStr"/>
       <c r="Q94" s="15" t="inlineStr"/>
       <c r="R94" s="15" t="inlineStr"/>
+      <c r="S94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
@@ -7743,6 +8042,7 @@
       <c r="P95" s="15" t="inlineStr"/>
       <c r="Q95" s="15" t="inlineStr"/>
       <c r="R95" s="15" t="inlineStr"/>
+      <c r="S95" s="12" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -7799,6 +8099,7 @@
       <c r="P96" s="15" t="inlineStr"/>
       <c r="Q96" s="15" t="inlineStr"/>
       <c r="R96" s="15" t="inlineStr"/>
+      <c r="S96" s="12" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
@@ -7875,6 +8176,11 @@
       <c r="P97" s="8" t="inlineStr"/>
       <c r="Q97" s="8" t="inlineStr"/>
       <c r="R97" s="8" t="inlineStr"/>
+      <c r="S97" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
@@ -7947,6 +8253,11 @@
       <c r="P98" s="8" t="inlineStr"/>
       <c r="Q98" s="8" t="inlineStr"/>
       <c r="R98" s="8" t="inlineStr"/>
+      <c r="S98" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
@@ -8019,6 +8330,7 @@
       <c r="P99" s="15" t="inlineStr"/>
       <c r="Q99" s="15" t="inlineStr"/>
       <c r="R99" s="15" t="inlineStr"/>
+      <c r="S99" s="12" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
@@ -8087,6 +8399,7 @@
       <c r="P100" s="15" t="inlineStr"/>
       <c r="Q100" s="15" t="inlineStr"/>
       <c r="R100" s="15" t="inlineStr"/>
+      <c r="S100" s="12" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
@@ -8159,6 +8472,11 @@
       <c r="P101" s="8" t="inlineStr"/>
       <c r="Q101" s="8" t="inlineStr"/>
       <c r="R101" s="8" t="inlineStr"/>
+      <c r="S101" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
@@ -8235,6 +8553,11 @@
       <c r="P102" s="8" t="inlineStr"/>
       <c r="Q102" s="8" t="inlineStr"/>
       <c r="R102" s="8" t="inlineStr"/>
+      <c r="S102" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
@@ -8303,6 +8626,11 @@
       <c r="P103" s="8" t="inlineStr"/>
       <c r="Q103" s="8" t="inlineStr"/>
       <c r="R103" s="8" t="inlineStr"/>
+      <c r="S103" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -8379,6 +8707,11 @@
       <c r="P104" s="8" t="inlineStr"/>
       <c r="Q104" s="8" t="inlineStr"/>
       <c r="R104" s="8" t="inlineStr"/>
+      <c r="S104" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
@@ -8451,6 +8784,11 @@
       <c r="P105" s="8" t="inlineStr"/>
       <c r="Q105" s="8" t="inlineStr"/>
       <c r="R105" s="8" t="inlineStr"/>
+      <c r="S105" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
@@ -8539,6 +8877,11 @@
         </is>
       </c>
       <c r="R106" s="8" t="inlineStr"/>
+      <c r="S106" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
@@ -8615,6 +8958,11 @@
       <c r="P107" s="8" t="inlineStr"/>
       <c r="Q107" s="8" t="inlineStr"/>
       <c r="R107" s="8" t="inlineStr"/>
+      <c r="S107" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
@@ -8683,6 +9031,7 @@
       <c r="P108" s="15" t="inlineStr"/>
       <c r="Q108" s="15" t="inlineStr"/>
       <c r="R108" s="15" t="inlineStr"/>
+      <c r="S108" s="12" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
@@ -8739,6 +9088,7 @@
       <c r="P109" s="15" t="inlineStr"/>
       <c r="Q109" s="15" t="inlineStr"/>
       <c r="R109" s="15" t="inlineStr"/>
+      <c r="S109" s="12" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -8823,6 +9173,11 @@
         </is>
       </c>
       <c r="R110" s="8" t="inlineStr"/>
+      <c r="S110" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
@@ -8903,6 +9258,11 @@
         </is>
       </c>
       <c r="R111" s="8" t="inlineStr"/>
+      <c r="S111" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
@@ -8979,6 +9339,11 @@
       <c r="P112" s="8" t="inlineStr"/>
       <c r="Q112" s="8" t="inlineStr"/>
       <c r="R112" s="8" t="inlineStr"/>
+      <c r="S112" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
@@ -9055,6 +9420,11 @@
       <c r="P113" s="8" t="inlineStr"/>
       <c r="Q113" s="8" t="inlineStr"/>
       <c r="R113" s="8" t="inlineStr"/>
+      <c r="S113" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
@@ -9131,6 +9501,11 @@
       <c r="P114" s="8" t="inlineStr"/>
       <c r="Q114" s="8" t="inlineStr"/>
       <c r="R114" s="8" t="inlineStr"/>
+      <c r="S114" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
@@ -9203,6 +9578,11 @@
       <c r="P115" s="8" t="inlineStr"/>
       <c r="Q115" s="8" t="inlineStr"/>
       <c r="R115" s="8" t="inlineStr"/>
+      <c r="S115" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -9271,6 +9651,7 @@
       <c r="P116" s="15" t="inlineStr"/>
       <c r="Q116" s="15" t="inlineStr"/>
       <c r="R116" s="15" t="inlineStr"/>
+      <c r="S116" s="12" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
@@ -9327,6 +9708,7 @@
       <c r="P117" s="15" t="inlineStr"/>
       <c r="Q117" s="15" t="inlineStr"/>
       <c r="R117" s="15" t="inlineStr"/>
+      <c r="S117" s="12" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -9395,6 +9777,7 @@
       <c r="P118" s="15" t="inlineStr"/>
       <c r="Q118" s="15" t="inlineStr"/>
       <c r="R118" s="15" t="inlineStr"/>
+      <c r="S118" s="12" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
@@ -9455,6 +9838,7 @@
       <c r="P119" s="15" t="inlineStr"/>
       <c r="Q119" s="15" t="inlineStr"/>
       <c r="R119" s="15" t="inlineStr"/>
+      <c r="S119" s="12" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -9523,6 +9907,7 @@
       <c r="P120" s="15" t="inlineStr"/>
       <c r="Q120" s="15" t="inlineStr"/>
       <c r="R120" s="15" t="inlineStr"/>
+      <c r="S120" s="12" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
@@ -9579,6 +9964,7 @@
       <c r="P121" s="15" t="inlineStr"/>
       <c r="Q121" s="15" t="inlineStr"/>
       <c r="R121" s="15" t="inlineStr"/>
+      <c r="S121" s="12" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
@@ -9655,6 +10041,11 @@
       <c r="P122" s="8" t="inlineStr"/>
       <c r="Q122" s="8" t="inlineStr"/>
       <c r="R122" s="8" t="inlineStr"/>
+      <c r="S122" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
@@ -9727,6 +10118,11 @@
       <c r="P123" s="8" t="inlineStr"/>
       <c r="Q123" s="8" t="inlineStr"/>
       <c r="R123" s="8" t="inlineStr"/>
+      <c r="S123" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
@@ -9803,6 +10199,11 @@
       <c r="P124" s="8" t="inlineStr"/>
       <c r="Q124" s="8" t="inlineStr"/>
       <c r="R124" s="8" t="inlineStr"/>
+      <c r="S124" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
@@ -9875,6 +10276,11 @@
       <c r="P125" s="8" t="inlineStr"/>
       <c r="Q125" s="8" t="inlineStr"/>
       <c r="R125" s="8" t="inlineStr"/>
+      <c r="S125" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
@@ -9943,6 +10349,7 @@
       <c r="P126" s="15" t="inlineStr"/>
       <c r="Q126" s="15" t="inlineStr"/>
       <c r="R126" s="15" t="inlineStr"/>
+      <c r="S126" s="12" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
@@ -9999,6 +10406,7 @@
       <c r="P127" s="15" t="inlineStr"/>
       <c r="Q127" s="15" t="inlineStr"/>
       <c r="R127" s="15" t="inlineStr"/>
+      <c r="S127" s="12" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
@@ -10071,6 +10479,7 @@
       <c r="P128" s="15" t="inlineStr"/>
       <c r="Q128" s="15" t="inlineStr"/>
       <c r="R128" s="15" t="inlineStr"/>
+      <c r="S128" s="12" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
@@ -10139,6 +10548,7 @@
       <c r="P129" s="15" t="inlineStr"/>
       <c r="Q129" s="15" t="inlineStr"/>
       <c r="R129" s="15" t="inlineStr"/>
+      <c r="S129" s="12" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
@@ -10207,6 +10617,7 @@
       <c r="P130" s="15" t="inlineStr"/>
       <c r="Q130" s="15" t="inlineStr"/>
       <c r="R130" s="15" t="inlineStr"/>
+      <c r="S130" s="12" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="inlineStr">
@@ -10263,6 +10674,7 @@
       <c r="P131" s="15" t="inlineStr"/>
       <c r="Q131" s="15" t="inlineStr"/>
       <c r="R131" s="15" t="inlineStr"/>
+      <c r="S131" s="12" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
@@ -10343,6 +10755,11 @@
       <c r="P132" s="8" t="inlineStr"/>
       <c r="Q132" s="8" t="inlineStr"/>
       <c r="R132" s="8" t="inlineStr"/>
+      <c r="S132" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="12" t="inlineStr">
@@ -10419,6 +10836,11 @@
       <c r="P133" s="8" t="inlineStr"/>
       <c r="Q133" s="8" t="inlineStr"/>
       <c r="R133" s="8" t="inlineStr"/>
+      <c r="S133" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
@@ -10495,6 +10917,11 @@
       <c r="P134" s="8" t="inlineStr"/>
       <c r="Q134" s="8" t="inlineStr"/>
       <c r="R134" s="8" t="inlineStr"/>
+      <c r="S134" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="12" t="inlineStr">
@@ -10571,6 +10998,11 @@
       <c r="P135" s="8" t="inlineStr"/>
       <c r="Q135" s="8" t="inlineStr"/>
       <c r="R135" s="8" t="inlineStr"/>
+      <c r="S135" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
@@ -10647,6 +11079,11 @@
       <c r="P136" s="8" t="inlineStr"/>
       <c r="Q136" s="8" t="inlineStr"/>
       <c r="R136" s="8" t="inlineStr"/>
+      <c r="S136" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
@@ -10723,6 +11160,11 @@
       <c r="P137" s="8" t="inlineStr"/>
       <c r="Q137" s="8" t="inlineStr"/>
       <c r="R137" s="8" t="inlineStr"/>
+      <c r="S137" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
@@ -10803,6 +11245,11 @@
         </is>
       </c>
       <c r="R138" s="8" t="inlineStr"/>
+      <c r="S138" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
@@ -10887,6 +11334,11 @@
         </is>
       </c>
       <c r="R139" s="8" t="inlineStr"/>
+      <c r="S139" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
@@ -10967,6 +11419,11 @@
         </is>
       </c>
       <c r="R140" s="8" t="inlineStr"/>
+      <c r="S140" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="12" t="inlineStr">
@@ -11051,6 +11508,11 @@
         </is>
       </c>
       <c r="R141" s="8" t="inlineStr"/>
+      <c r="S141" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
@@ -11131,6 +11593,11 @@
         </is>
       </c>
       <c r="R142" s="8" t="inlineStr"/>
+      <c r="S142" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="12" t="inlineStr">
@@ -11211,6 +11678,11 @@
       <c r="P143" s="8" t="inlineStr"/>
       <c r="Q143" s="8" t="inlineStr"/>
       <c r="R143" s="8" t="inlineStr"/>
+      <c r="S143" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="12" t="inlineStr">
@@ -11291,6 +11763,11 @@
       <c r="P144" s="8" t="inlineStr"/>
       <c r="Q144" s="8" t="inlineStr"/>
       <c r="R144" s="8" t="inlineStr"/>
+      <c r="S144" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="12" t="inlineStr">
@@ -11359,6 +11836,7 @@
       <c r="P145" s="15" t="inlineStr"/>
       <c r="Q145" s="15" t="inlineStr"/>
       <c r="R145" s="15" t="inlineStr"/>
+      <c r="S145" s="12" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
@@ -11419,6 +11897,7 @@
       <c r="P146" s="15" t="inlineStr"/>
       <c r="Q146" s="15" t="inlineStr"/>
       <c r="R146" s="15" t="inlineStr"/>
+      <c r="S146" s="12" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="12" t="inlineStr">
@@ -11503,6 +11982,11 @@
         </is>
       </c>
       <c r="R147" s="8" t="inlineStr"/>
+      <c r="S147" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="12" t="inlineStr">
@@ -11583,6 +12067,11 @@
         </is>
       </c>
       <c r="R148" s="8" t="inlineStr"/>
+      <c r="S148" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="12" t="inlineStr">
@@ -11651,6 +12140,7 @@
       <c r="P149" s="15" t="inlineStr"/>
       <c r="Q149" s="15" t="inlineStr"/>
       <c r="R149" s="15" t="inlineStr"/>
+      <c r="S149" s="12" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
@@ -11707,6 +12197,7 @@
       <c r="P150" s="15" t="inlineStr"/>
       <c r="Q150" s="15" t="inlineStr"/>
       <c r="R150" s="15" t="inlineStr"/>
+      <c r="S150" s="12" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="12" t="inlineStr">
@@ -11775,6 +12266,7 @@
       <c r="P151" s="15" t="inlineStr"/>
       <c r="Q151" s="15" t="inlineStr"/>
       <c r="R151" s="15" t="inlineStr"/>
+      <c r="S151" s="12" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="12" t="inlineStr">
@@ -11831,6 +12323,7 @@
       <c r="P152" s="15" t="inlineStr"/>
       <c r="Q152" s="15" t="inlineStr"/>
       <c r="R152" s="15" t="inlineStr"/>
+      <c r="S152" s="12" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="12" t="inlineStr">
@@ -11907,6 +12400,11 @@
       <c r="P153" s="8" t="inlineStr"/>
       <c r="Q153" s="8" t="inlineStr"/>
       <c r="R153" s="8" t="inlineStr"/>
+      <c r="S153" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="12" t="inlineStr">
@@ -11983,6 +12481,11 @@
       <c r="P154" s="8" t="inlineStr"/>
       <c r="Q154" s="8" t="inlineStr"/>
       <c r="R154" s="8" t="inlineStr"/>
+      <c r="S154" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="12" t="inlineStr">
@@ -12051,6 +12554,7 @@
       <c r="P155" s="15" t="inlineStr"/>
       <c r="Q155" s="15" t="inlineStr"/>
       <c r="R155" s="15" t="inlineStr"/>
+      <c r="S155" s="12" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="12" t="inlineStr">
@@ -12107,6 +12611,7 @@
       <c r="P156" s="15" t="inlineStr"/>
       <c r="Q156" s="15" t="inlineStr"/>
       <c r="R156" s="15" t="inlineStr"/>
+      <c r="S156" s="12" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="12" t="inlineStr">
@@ -12191,6 +12696,11 @@
         </is>
       </c>
       <c r="R157" s="8" t="inlineStr"/>
+      <c r="S157" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="12" t="inlineStr">
@@ -12275,6 +12785,11 @@
         </is>
       </c>
       <c r="R158" s="8" t="inlineStr"/>
+      <c r="S158" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="12" t="inlineStr">
@@ -12359,6 +12874,11 @@
         </is>
       </c>
       <c r="R159" s="8" t="inlineStr"/>
+      <c r="S159" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="12" t="inlineStr">
@@ -12427,6 +12947,7 @@
       <c r="P160" s="15" t="inlineStr"/>
       <c r="Q160" s="15" t="inlineStr"/>
       <c r="R160" s="15" t="inlineStr"/>
+      <c r="S160" s="12" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="12" t="inlineStr">
@@ -12483,6 +13004,7 @@
       <c r="P161" s="15" t="inlineStr"/>
       <c r="Q161" s="15" t="inlineStr"/>
       <c r="R161" s="15" t="inlineStr"/>
+      <c r="S161" s="12" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="12" t="inlineStr">
@@ -12563,6 +13085,11 @@
         </is>
       </c>
       <c r="R162" s="8" t="inlineStr"/>
+      <c r="S162" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="12" t="inlineStr">
@@ -12635,6 +13162,11 @@
         </is>
       </c>
       <c r="R163" s="8" t="inlineStr"/>
+      <c r="S163" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="12" t="inlineStr">
@@ -12711,6 +13243,11 @@
       <c r="P164" s="8" t="inlineStr"/>
       <c r="Q164" s="8" t="inlineStr"/>
       <c r="R164" s="8" t="inlineStr"/>
+      <c r="S164" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="12" t="inlineStr">
@@ -12787,6 +13324,11 @@
       <c r="P165" s="8" t="inlineStr"/>
       <c r="Q165" s="8" t="inlineStr"/>
       <c r="R165" s="8" t="inlineStr"/>
+      <c r="S165" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="12" t="inlineStr">
@@ -12855,6 +13397,7 @@
       <c r="P166" s="15" t="inlineStr"/>
       <c r="Q166" s="15" t="inlineStr"/>
       <c r="R166" s="15" t="inlineStr"/>
+      <c r="S166" s="12" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="12" t="inlineStr">
@@ -12915,6 +13458,7 @@
       <c r="P167" s="15" t="inlineStr"/>
       <c r="Q167" s="15" t="inlineStr"/>
       <c r="R167" s="15" t="inlineStr"/>
+      <c r="S167" s="12" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="12" t="inlineStr">
@@ -12987,6 +13531,7 @@
       <c r="P168" s="15" t="inlineStr"/>
       <c r="Q168" s="15" t="inlineStr"/>
       <c r="R168" s="15" t="inlineStr"/>
+      <c r="S168" s="12" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="12" t="inlineStr">
@@ -13055,6 +13600,7 @@
       <c r="P169" s="15" t="inlineStr"/>
       <c r="Q169" s="15" t="inlineStr"/>
       <c r="R169" s="15" t="inlineStr"/>
+      <c r="S169" s="12" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="12" t="inlineStr">
@@ -13123,6 +13669,7 @@
       <c r="P170" s="15" t="inlineStr"/>
       <c r="Q170" s="15" t="inlineStr"/>
       <c r="R170" s="15" t="inlineStr"/>
+      <c r="S170" s="12" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="12" t="inlineStr">
@@ -13179,6 +13726,7 @@
       <c r="P171" s="15" t="inlineStr"/>
       <c r="Q171" s="15" t="inlineStr"/>
       <c r="R171" s="15" t="inlineStr"/>
+      <c r="S171" s="12" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="12" t="inlineStr">
@@ -13259,6 +13807,11 @@
       <c r="P172" s="8" t="inlineStr"/>
       <c r="Q172" s="8" t="inlineStr"/>
       <c r="R172" s="8" t="inlineStr"/>
+      <c r="S172" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="12" t="inlineStr">
@@ -13335,6 +13888,11 @@
       <c r="P173" s="8" t="inlineStr"/>
       <c r="Q173" s="8" t="inlineStr"/>
       <c r="R173" s="8" t="inlineStr"/>
+      <c r="S173" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="12" t="inlineStr">
@@ -13411,6 +13969,11 @@
       <c r="P174" s="8" t="inlineStr"/>
       <c r="Q174" s="8" t="inlineStr"/>
       <c r="R174" s="8" t="inlineStr"/>
+      <c r="S174" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="12" t="inlineStr">
@@ -13487,6 +14050,11 @@
       <c r="P175" s="8" t="inlineStr"/>
       <c r="Q175" s="8" t="inlineStr"/>
       <c r="R175" s="8" t="inlineStr"/>
+      <c r="S175" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
@@ -13563,6 +14131,11 @@
       <c r="P176" s="8" t="inlineStr"/>
       <c r="Q176" s="8" t="inlineStr"/>
       <c r="R176" s="8" t="inlineStr"/>
+      <c r="S176" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="12" t="inlineStr">
@@ -13635,6 +14208,7 @@
       <c r="P177" s="15" t="inlineStr"/>
       <c r="Q177" s="15" t="inlineStr"/>
       <c r="R177" s="15" t="inlineStr"/>
+      <c r="S177" s="12" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="12" t="inlineStr">
@@ -13703,6 +14277,7 @@
       <c r="P178" s="15" t="inlineStr"/>
       <c r="Q178" s="15" t="inlineStr"/>
       <c r="R178" s="15" t="inlineStr"/>
+      <c r="S178" s="12" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="12" t="inlineStr">
@@ -13771,6 +14346,7 @@
       <c r="P179" s="15" t="inlineStr"/>
       <c r="Q179" s="15" t="inlineStr"/>
       <c r="R179" s="15" t="inlineStr"/>
+      <c r="S179" s="12" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="12" t="inlineStr">
@@ -13827,6 +14403,7 @@
       <c r="P180" s="15" t="inlineStr"/>
       <c r="Q180" s="15" t="inlineStr"/>
       <c r="R180" s="15" t="inlineStr"/>
+      <c r="S180" s="12" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="12" t="inlineStr">
@@ -13899,6 +14476,7 @@
       <c r="P181" s="15" t="inlineStr"/>
       <c r="Q181" s="15" t="inlineStr"/>
       <c r="R181" s="15" t="inlineStr"/>
+      <c r="S181" s="12" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="12" t="inlineStr">
@@ -13967,6 +14545,7 @@
       <c r="P182" s="15" t="inlineStr"/>
       <c r="Q182" s="15" t="inlineStr"/>
       <c r="R182" s="15" t="inlineStr"/>
+      <c r="S182" s="12" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="12" t="inlineStr">
@@ -14039,6 +14618,7 @@
       <c r="P183" s="15" t="inlineStr"/>
       <c r="Q183" s="15" t="inlineStr"/>
       <c r="R183" s="15" t="inlineStr"/>
+      <c r="S183" s="12" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="12" t="inlineStr">
@@ -14107,6 +14687,7 @@
       <c r="P184" s="15" t="inlineStr"/>
       <c r="Q184" s="15" t="inlineStr"/>
       <c r="R184" s="15" t="inlineStr"/>
+      <c r="S184" s="12" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="inlineStr">
@@ -14183,6 +14764,11 @@
       <c r="P185" s="8" t="inlineStr"/>
       <c r="Q185" s="8" t="inlineStr"/>
       <c r="R185" s="8" t="inlineStr"/>
+      <c r="S185" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="12" t="inlineStr">
@@ -14255,6 +14841,11 @@
       <c r="P186" s="8" t="inlineStr"/>
       <c r="Q186" s="8" t="inlineStr"/>
       <c r="R186" s="8" t="inlineStr"/>
+      <c r="S186" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="12" t="inlineStr">
@@ -14323,6 +14914,7 @@
       <c r="P187" s="15" t="inlineStr"/>
       <c r="Q187" s="15" t="inlineStr"/>
       <c r="R187" s="15" t="inlineStr"/>
+      <c r="S187" s="12" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="12" t="inlineStr">
@@ -14379,6 +14971,7 @@
       <c r="P188" s="15" t="inlineStr"/>
       <c r="Q188" s="15" t="inlineStr"/>
       <c r="R188" s="15" t="inlineStr"/>
+      <c r="S188" s="12" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="12" t="inlineStr">
@@ -14447,6 +15040,7 @@
       <c r="P189" s="15" t="inlineStr"/>
       <c r="Q189" s="15" t="inlineStr"/>
       <c r="R189" s="15" t="inlineStr"/>
+      <c r="S189" s="12" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="12" t="inlineStr">
@@ -14515,6 +15109,7 @@
       <c r="P190" s="15" t="inlineStr"/>
       <c r="Q190" s="15" t="inlineStr"/>
       <c r="R190" s="15" t="inlineStr"/>
+      <c r="S190" s="12" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="12" t="inlineStr">
@@ -14583,6 +15178,7 @@
       <c r="P191" s="15" t="inlineStr"/>
       <c r="Q191" s="15" t="inlineStr"/>
       <c r="R191" s="15" t="inlineStr"/>
+      <c r="S191" s="12" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="12" t="inlineStr">
@@ -14643,6 +15239,7 @@
       <c r="P192" s="15" t="inlineStr"/>
       <c r="Q192" s="15" t="inlineStr"/>
       <c r="R192" s="15" t="inlineStr"/>
+      <c r="S192" s="12" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="12" t="inlineStr">
@@ -14715,6 +15312,7 @@
       <c r="P193" s="15" t="inlineStr"/>
       <c r="Q193" s="15" t="inlineStr"/>
       <c r="R193" s="15" t="inlineStr"/>
+      <c r="S193" s="12" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="12" t="inlineStr">
@@ -14783,6 +15381,7 @@
       <c r="P194" s="15" t="inlineStr"/>
       <c r="Q194" s="15" t="inlineStr"/>
       <c r="R194" s="15" t="inlineStr"/>
+      <c r="S194" s="12" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="12" t="inlineStr">
@@ -14859,6 +15458,11 @@
       <c r="P195" s="8" t="inlineStr"/>
       <c r="Q195" s="8" t="inlineStr"/>
       <c r="R195" s="8" t="inlineStr"/>
+      <c r="S195" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="12" t="inlineStr">
@@ -14935,6 +15539,11 @@
       <c r="P196" s="8" t="inlineStr"/>
       <c r="Q196" s="8" t="inlineStr"/>
       <c r="R196" s="8" t="inlineStr"/>
+      <c r="S196" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="12" t="inlineStr">
@@ -15003,6 +15612,7 @@
       <c r="P197" s="15" t="inlineStr"/>
       <c r="Q197" s="15" t="inlineStr"/>
       <c r="R197" s="15" t="inlineStr"/>
+      <c r="S197" s="12" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="12" t="inlineStr">
@@ -15059,6 +15669,7 @@
       <c r="P198" s="15" t="inlineStr"/>
       <c r="Q198" s="15" t="inlineStr"/>
       <c r="R198" s="15" t="inlineStr"/>
+      <c r="S198" s="12" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="12" t="inlineStr">
@@ -15131,6 +15742,7 @@
       <c r="P199" s="15" t="inlineStr"/>
       <c r="Q199" s="15" t="inlineStr"/>
       <c r="R199" s="15" t="inlineStr"/>
+      <c r="S199" s="12" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="12" t="inlineStr">
@@ -15199,6 +15811,7 @@
       <c r="P200" s="15" t="inlineStr"/>
       <c r="Q200" s="15" t="inlineStr"/>
       <c r="R200" s="15" t="inlineStr"/>
+      <c r="S200" s="12" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="12" t="inlineStr">
@@ -15275,6 +15888,11 @@
       <c r="P201" s="8" t="inlineStr"/>
       <c r="Q201" s="8" t="inlineStr"/>
       <c r="R201" s="8" t="inlineStr"/>
+      <c r="S201" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="12" t="inlineStr">
@@ -15343,6 +15961,11 @@
       <c r="P202" s="8" t="inlineStr"/>
       <c r="Q202" s="8" t="inlineStr"/>
       <c r="R202" s="8" t="inlineStr"/>
+      <c r="S202" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="12" t="inlineStr">
@@ -15411,6 +16034,7 @@
       <c r="P203" s="15" t="inlineStr"/>
       <c r="Q203" s="15" t="inlineStr"/>
       <c r="R203" s="15" t="inlineStr"/>
+      <c r="S203" s="12" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="12" t="inlineStr">
@@ -15467,6 +16091,7 @@
       <c r="P204" s="15" t="inlineStr"/>
       <c r="Q204" s="15" t="inlineStr"/>
       <c r="R204" s="15" t="inlineStr"/>
+      <c r="S204" s="12" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="12" t="inlineStr">
@@ -15539,6 +16164,7 @@
       <c r="P205" s="15" t="inlineStr"/>
       <c r="Q205" s="15" t="inlineStr"/>
       <c r="R205" s="15" t="inlineStr"/>
+      <c r="S205" s="12" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="12" t="inlineStr">
@@ -15607,6 +16233,7 @@
       <c r="P206" s="15" t="inlineStr"/>
       <c r="Q206" s="15" t="inlineStr"/>
       <c r="R206" s="15" t="inlineStr"/>
+      <c r="S206" s="12" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="12" t="inlineStr">
@@ -15683,6 +16310,11 @@
       <c r="P207" s="8" t="inlineStr"/>
       <c r="Q207" s="8" t="inlineStr"/>
       <c r="R207" s="8" t="inlineStr"/>
+      <c r="S207" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="12" t="inlineStr">
@@ -15759,6 +16391,11 @@
       <c r="P208" s="8" t="inlineStr"/>
       <c r="Q208" s="8" t="inlineStr"/>
       <c r="R208" s="8" t="inlineStr"/>
+      <c r="S208" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="12" t="inlineStr">
@@ -15827,6 +16464,7 @@
       <c r="P209" s="15" t="inlineStr"/>
       <c r="Q209" s="15" t="inlineStr"/>
       <c r="R209" s="15" t="inlineStr"/>
+      <c r="S209" s="12" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="12" t="inlineStr">
@@ -15883,6 +16521,7 @@
       <c r="P210" s="15" t="inlineStr"/>
       <c r="Q210" s="15" t="inlineStr"/>
       <c r="R210" s="15" t="inlineStr"/>
+      <c r="S210" s="12" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="12" t="inlineStr">
@@ -15955,6 +16594,7 @@
       <c r="P211" s="15" t="inlineStr"/>
       <c r="Q211" s="15" t="inlineStr"/>
       <c r="R211" s="15" t="inlineStr"/>
+      <c r="S211" s="12" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="12" t="inlineStr">
@@ -16023,6 +16663,7 @@
       <c r="P212" s="15" t="inlineStr"/>
       <c r="Q212" s="15" t="inlineStr"/>
       <c r="R212" s="15" t="inlineStr"/>
+      <c r="S212" s="12" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="12" t="inlineStr">
@@ -16107,6 +16748,11 @@
         </is>
       </c>
       <c r="R213" s="8" t="inlineStr"/>
+      <c r="S213" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="12" t="inlineStr">
@@ -16191,6 +16837,11 @@
         </is>
       </c>
       <c r="R214" s="8" t="inlineStr"/>
+      <c r="S214" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="12" t="inlineStr">
@@ -16271,6 +16922,11 @@
         </is>
       </c>
       <c r="R215" s="8" t="inlineStr"/>
+      <c r="S215" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="12" t="inlineStr">
@@ -16347,6 +17003,11 @@
       <c r="P216" s="8" t="inlineStr"/>
       <c r="Q216" s="8" t="inlineStr"/>
       <c r="R216" s="8" t="inlineStr"/>
+      <c r="S216" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="12" t="inlineStr">
@@ -16427,6 +17088,11 @@
         </is>
       </c>
       <c r="R217" s="8" t="inlineStr"/>
+      <c r="S217" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="12" t="inlineStr">
@@ -16507,6 +17173,11 @@
       <c r="P218" s="8" t="inlineStr"/>
       <c r="Q218" s="8" t="inlineStr"/>
       <c r="R218" s="8" t="inlineStr"/>
+      <c r="S218" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="12" t="inlineStr">
@@ -16583,6 +17254,11 @@
       <c r="P219" s="8" t="inlineStr"/>
       <c r="Q219" s="8" t="inlineStr"/>
       <c r="R219" s="8" t="inlineStr"/>
+      <c r="S219" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="12" t="inlineStr">
@@ -16651,6 +17327,7 @@
       <c r="P220" s="15" t="inlineStr"/>
       <c r="Q220" s="15" t="inlineStr"/>
       <c r="R220" s="15" t="inlineStr"/>
+      <c r="S220" s="12" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="12" t="inlineStr">
@@ -16723,6 +17400,7 @@
       <c r="P221" s="15" t="inlineStr"/>
       <c r="Q221" s="15" t="inlineStr"/>
       <c r="R221" s="15" t="inlineStr"/>
+      <c r="S221" s="12" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="12" t="inlineStr">
@@ -16795,6 +17473,7 @@
       <c r="P222" s="15" t="inlineStr"/>
       <c r="Q222" s="15" t="inlineStr"/>
       <c r="R222" s="15" t="inlineStr"/>
+      <c r="S222" s="12" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="12" t="inlineStr">
@@ -16863,6 +17542,7 @@
       <c r="P223" s="15" t="inlineStr"/>
       <c r="Q223" s="15" t="inlineStr"/>
       <c r="R223" s="15" t="inlineStr"/>
+      <c r="S223" s="12" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="12" t="inlineStr">
@@ -16939,6 +17619,11 @@
       <c r="P224" s="8" t="inlineStr"/>
       <c r="Q224" s="8" t="inlineStr"/>
       <c r="R224" s="8" t="inlineStr"/>
+      <c r="S224" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="12" t="inlineStr">
@@ -17015,6 +17700,11 @@
       <c r="P225" s="8" t="inlineStr"/>
       <c r="Q225" s="8" t="inlineStr"/>
       <c r="R225" s="8" t="inlineStr"/>
+      <c r="S225" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="12" t="inlineStr">
@@ -17083,6 +17773,7 @@
       <c r="P226" s="15" t="inlineStr"/>
       <c r="Q226" s="15" t="inlineStr"/>
       <c r="R226" s="15" t="inlineStr"/>
+      <c r="S226" s="12" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="12" t="inlineStr">
@@ -17139,6 +17830,7 @@
       <c r="P227" s="15" t="inlineStr"/>
       <c r="Q227" s="15" t="inlineStr"/>
       <c r="R227" s="15" t="inlineStr"/>
+      <c r="S227" s="12" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="12" t="inlineStr">
@@ -17207,6 +17899,7 @@
       <c r="P228" s="15" t="inlineStr"/>
       <c r="Q228" s="15" t="inlineStr"/>
       <c r="R228" s="15" t="inlineStr"/>
+      <c r="S228" s="12" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="12" t="inlineStr">
@@ -17263,6 +17956,7 @@
       <c r="P229" s="15" t="inlineStr"/>
       <c r="Q229" s="15" t="inlineStr"/>
       <c r="R229" s="15" t="inlineStr"/>
+      <c r="S229" s="12" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="12" t="inlineStr">
@@ -17343,6 +18037,11 @@
       <c r="P230" s="8" t="inlineStr"/>
       <c r="Q230" s="8" t="inlineStr"/>
       <c r="R230" s="8" t="inlineStr"/>
+      <c r="S230" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="12" t="inlineStr">
@@ -17419,6 +18118,11 @@
       <c r="P231" s="8" t="inlineStr"/>
       <c r="Q231" s="8" t="inlineStr"/>
       <c r="R231" s="8" t="inlineStr"/>
+      <c r="S231" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="12" t="inlineStr">
@@ -17495,6 +18199,11 @@
       <c r="P232" s="8" t="inlineStr"/>
       <c r="Q232" s="8" t="inlineStr"/>
       <c r="R232" s="8" t="inlineStr"/>
+      <c r="S232" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="12" t="inlineStr">
@@ -17571,6 +18280,11 @@
       <c r="P233" s="8" t="inlineStr"/>
       <c r="Q233" s="8" t="inlineStr"/>
       <c r="R233" s="8" t="inlineStr"/>
+      <c r="S233" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="12" t="inlineStr">
@@ -17651,6 +18365,11 @@
       <c r="P234" s="8" t="inlineStr"/>
       <c r="Q234" s="8" t="inlineStr"/>
       <c r="R234" s="8" t="inlineStr"/>
+      <c r="S234" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="12" t="inlineStr">
@@ -17727,6 +18446,11 @@
       <c r="P235" s="8" t="inlineStr"/>
       <c r="Q235" s="8" t="inlineStr"/>
       <c r="R235" s="8" t="inlineStr"/>
+      <c r="S235" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="12" t="inlineStr">
@@ -17807,6 +18531,11 @@
         </is>
       </c>
       <c r="R236" s="8" t="inlineStr"/>
+      <c r="S236" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="12" t="inlineStr">
@@ -17879,6 +18608,11 @@
         </is>
       </c>
       <c r="R237" s="8" t="inlineStr"/>
+      <c r="S237" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="12" t="inlineStr">
@@ -17947,6 +18681,7 @@
       <c r="P238" s="15" t="inlineStr"/>
       <c r="Q238" s="15" t="inlineStr"/>
       <c r="R238" s="15" t="inlineStr"/>
+      <c r="S238" s="12" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="12" t="inlineStr">
@@ -18019,6 +18754,7 @@
       <c r="P239" s="15" t="inlineStr"/>
       <c r="Q239" s="15" t="inlineStr"/>
       <c r="R239" s="15" t="inlineStr"/>
+      <c r="S239" s="12" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="12" t="inlineStr">
@@ -18095,6 +18831,11 @@
       <c r="P240" s="8" t="inlineStr"/>
       <c r="Q240" s="8" t="inlineStr"/>
       <c r="R240" s="8" t="inlineStr"/>
+      <c r="S240" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="12" t="inlineStr">
@@ -18171,6 +18912,11 @@
       <c r="P241" s="8" t="inlineStr"/>
       <c r="Q241" s="8" t="inlineStr"/>
       <c r="R241" s="8" t="inlineStr"/>
+      <c r="S241" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="12" t="inlineStr">
@@ -18251,6 +18997,11 @@
       <c r="P242" s="8" t="inlineStr"/>
       <c r="Q242" s="8" t="inlineStr"/>
       <c r="R242" s="8" t="inlineStr"/>
+      <c r="S242" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="12" t="inlineStr">
@@ -18327,6 +19078,11 @@
       <c r="P243" s="8" t="inlineStr"/>
       <c r="Q243" s="8" t="inlineStr"/>
       <c r="R243" s="8" t="inlineStr"/>
+      <c r="S243" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="12" t="inlineStr">
@@ -18407,6 +19163,11 @@
       <c r="P244" s="8" t="inlineStr"/>
       <c r="Q244" s="8" t="inlineStr"/>
       <c r="R244" s="8" t="inlineStr"/>
+      <c r="S244" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="12" t="inlineStr">
@@ -18483,6 +19244,11 @@
       <c r="P245" s="8" t="inlineStr"/>
       <c r="Q245" s="8" t="inlineStr"/>
       <c r="R245" s="8" t="inlineStr"/>
+      <c r="S245" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="12" t="inlineStr">
@@ -18555,6 +19321,11 @@
       <c r="P246" s="8" t="inlineStr"/>
       <c r="Q246" s="8" t="inlineStr"/>
       <c r="R246" s="8" t="inlineStr"/>
+      <c r="S246" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="12" t="inlineStr">
@@ -18631,6 +19402,11 @@
       <c r="P247" s="8" t="inlineStr"/>
       <c r="Q247" s="8" t="inlineStr"/>
       <c r="R247" s="8" t="inlineStr"/>
+      <c r="S247" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="12" t="inlineStr">
@@ -18707,6 +19483,11 @@
       <c r="P248" s="8" t="inlineStr"/>
       <c r="Q248" s="8" t="inlineStr"/>
       <c r="R248" s="8" t="inlineStr"/>
+      <c r="S248" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="12" t="inlineStr">
@@ -18787,6 +19568,11 @@
       <c r="P249" s="8" t="inlineStr"/>
       <c r="Q249" s="8" t="inlineStr"/>
       <c r="R249" s="8" t="inlineStr"/>
+      <c r="S249" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="12" t="inlineStr">
@@ -18867,6 +19653,11 @@
       <c r="P250" s="8" t="inlineStr"/>
       <c r="Q250" s="8" t="inlineStr"/>
       <c r="R250" s="8" t="inlineStr"/>
+      <c r="S250" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="12" t="inlineStr">
@@ -18935,6 +19726,7 @@
       <c r="P251" s="15" t="inlineStr"/>
       <c r="Q251" s="15" t="inlineStr"/>
       <c r="R251" s="15" t="inlineStr"/>
+      <c r="S251" s="12" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="12" t="inlineStr">
@@ -18991,6 +19783,7 @@
       <c r="P252" s="15" t="inlineStr"/>
       <c r="Q252" s="15" t="inlineStr"/>
       <c r="R252" s="15" t="inlineStr"/>
+      <c r="S252" s="12" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="12" t="inlineStr">
@@ -19059,6 +19852,7 @@
       <c r="P253" s="15" t="inlineStr"/>
       <c r="Q253" s="15" t="inlineStr"/>
       <c r="R253" s="15" t="inlineStr"/>
+      <c r="S253" s="12" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="12" t="inlineStr">
@@ -19115,6 +19909,7 @@
       <c r="P254" s="15" t="inlineStr"/>
       <c r="Q254" s="15" t="inlineStr"/>
       <c r="R254" s="15" t="inlineStr"/>
+      <c r="S254" s="12" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="12" t="inlineStr">
@@ -19183,6 +19978,7 @@
       <c r="P255" s="15" t="inlineStr"/>
       <c r="Q255" s="15" t="inlineStr"/>
       <c r="R255" s="15" t="inlineStr"/>
+      <c r="S255" s="12" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="12" t="inlineStr">
@@ -19239,6 +20035,7 @@
       <c r="P256" s="15" t="inlineStr"/>
       <c r="Q256" s="15" t="inlineStr"/>
       <c r="R256" s="15" t="inlineStr"/>
+      <c r="S256" s="12" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="12" t="inlineStr">
@@ -19311,6 +20108,7 @@
       <c r="P257" s="15" t="inlineStr"/>
       <c r="Q257" s="15" t="inlineStr"/>
       <c r="R257" s="15" t="inlineStr"/>
+      <c r="S257" s="12" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="12" t="inlineStr">
@@ -19379,6 +20177,7 @@
       <c r="P258" s="15" t="inlineStr"/>
       <c r="Q258" s="15" t="inlineStr"/>
       <c r="R258" s="15" t="inlineStr"/>
+      <c r="S258" s="12" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="12" t="inlineStr">
@@ -19455,6 +20254,11 @@
       <c r="P259" s="8" t="inlineStr"/>
       <c r="Q259" s="8" t="inlineStr"/>
       <c r="R259" s="8" t="inlineStr"/>
+      <c r="S259" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="12" t="inlineStr">
@@ -19531,6 +20335,11 @@
       <c r="P260" s="8" t="inlineStr"/>
       <c r="Q260" s="8" t="inlineStr"/>
       <c r="R260" s="8" t="inlineStr"/>
+      <c r="S260" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="12" t="inlineStr">
@@ -19611,6 +20420,11 @@
       <c r="P261" s="8" t="inlineStr"/>
       <c r="Q261" s="8" t="inlineStr"/>
       <c r="R261" s="8" t="inlineStr"/>
+      <c r="S261" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="12" t="inlineStr">
@@ -19687,6 +20501,11 @@
       <c r="P262" s="8" t="inlineStr"/>
       <c r="Q262" s="8" t="inlineStr"/>
       <c r="R262" s="8" t="inlineStr"/>
+      <c r="S262" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="12" t="inlineStr">
@@ -19767,6 +20586,11 @@
         </is>
       </c>
       <c r="R263" s="8" t="inlineStr"/>
+      <c r="S263" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="12" t="inlineStr">
@@ -19835,6 +20659,11 @@
         </is>
       </c>
       <c r="R264" s="8" t="inlineStr"/>
+      <c r="S264" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="12" t="inlineStr">
@@ -19903,6 +20732,7 @@
       <c r="P265" s="15" t="inlineStr"/>
       <c r="Q265" s="15" t="inlineStr"/>
       <c r="R265" s="15" t="inlineStr"/>
+      <c r="S265" s="12" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="12" t="inlineStr">
@@ -19959,6 +20789,7 @@
       <c r="P266" s="15" t="inlineStr"/>
       <c r="Q266" s="15" t="inlineStr"/>
       <c r="R266" s="15" t="inlineStr"/>
+      <c r="S266" s="12" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="12" t="inlineStr">
@@ -20027,6 +20858,7 @@
       <c r="P267" s="15" t="inlineStr"/>
       <c r="Q267" s="15" t="inlineStr"/>
       <c r="R267" s="15" t="inlineStr"/>
+      <c r="S267" s="12" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="12" t="inlineStr">
@@ -20087,6 +20919,7 @@
       <c r="P268" s="15" t="inlineStr"/>
       <c r="Q268" s="15" t="inlineStr"/>
       <c r="R268" s="15" t="inlineStr"/>
+      <c r="S268" s="12" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="12" t="inlineStr">
@@ -20167,6 +21000,11 @@
       <c r="P269" s="8" t="inlineStr"/>
       <c r="Q269" s="8" t="inlineStr"/>
       <c r="R269" s="8" t="inlineStr"/>
+      <c r="S269" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="12" t="inlineStr">
@@ -20243,6 +21081,11 @@
       <c r="P270" s="8" t="inlineStr"/>
       <c r="Q270" s="8" t="inlineStr"/>
       <c r="R270" s="8" t="inlineStr"/>
+      <c r="S270" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="12" t="inlineStr">
@@ -20311,6 +21154,7 @@
       <c r="P271" s="15" t="inlineStr"/>
       <c r="Q271" s="15" t="inlineStr"/>
       <c r="R271" s="15" t="inlineStr"/>
+      <c r="S271" s="12" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="12" t="inlineStr">
@@ -20367,6 +21211,7 @@
       <c r="P272" s="15" t="inlineStr"/>
       <c r="Q272" s="15" t="inlineStr"/>
       <c r="R272" s="15" t="inlineStr"/>
+      <c r="S272" s="12" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="12" t="inlineStr">
@@ -20447,6 +21292,11 @@
       <c r="P273" s="8" t="inlineStr"/>
       <c r="Q273" s="8" t="inlineStr"/>
       <c r="R273" s="8" t="inlineStr"/>
+      <c r="S273" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="12" t="inlineStr">
@@ -20527,6 +21377,11 @@
       <c r="P274" s="8" t="inlineStr"/>
       <c r="Q274" s="8" t="inlineStr"/>
       <c r="R274" s="8" t="inlineStr"/>
+      <c r="S274" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="12" t="inlineStr">
@@ -20607,6 +21462,11 @@
       <c r="P275" s="8" t="inlineStr"/>
       <c r="Q275" s="8" t="inlineStr"/>
       <c r="R275" s="8" t="inlineStr"/>
+      <c r="S275" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="12" t="inlineStr">
@@ -20695,6 +21555,11 @@
         </is>
       </c>
       <c r="R276" s="8" t="inlineStr"/>
+      <c r="S276" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="12" t="inlineStr">
@@ -20767,6 +21632,11 @@
       <c r="P277" s="8" t="inlineStr"/>
       <c r="Q277" s="8" t="inlineStr"/>
       <c r="R277" s="8" t="inlineStr"/>
+      <c r="S277" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="12" t="inlineStr">
@@ -20839,6 +21709,11 @@
       <c r="P278" s="8" t="inlineStr"/>
       <c r="Q278" s="8" t="inlineStr"/>
       <c r="R278" s="8" t="inlineStr"/>
+      <c r="S278" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="12" t="inlineStr">
@@ -20919,6 +21794,11 @@
         </is>
       </c>
       <c r="R279" s="8" t="inlineStr"/>
+      <c r="S279" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="12" t="inlineStr">
@@ -20987,6 +21867,11 @@
         </is>
       </c>
       <c r="R280" s="8" t="inlineStr"/>
+      <c r="S280" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="12" t="inlineStr">
@@ -21055,6 +21940,7 @@
       <c r="P281" s="15" t="inlineStr"/>
       <c r="Q281" s="15" t="inlineStr"/>
       <c r="R281" s="15" t="inlineStr"/>
+      <c r="S281" s="12" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="12" t="inlineStr">
@@ -21123,6 +22009,7 @@
       <c r="P282" s="15" t="inlineStr"/>
       <c r="Q282" s="15" t="inlineStr"/>
       <c r="R282" s="15" t="inlineStr"/>
+      <c r="S282" s="12" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="12" t="inlineStr">
@@ -21199,6 +22086,11 @@
       <c r="P283" s="8" t="inlineStr"/>
       <c r="Q283" s="8" t="inlineStr"/>
       <c r="R283" s="8" t="inlineStr"/>
+      <c r="S283" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="12" t="inlineStr">
@@ -21275,6 +22167,11 @@
       <c r="P284" s="8" t="inlineStr"/>
       <c r="Q284" s="8" t="inlineStr"/>
       <c r="R284" s="8" t="inlineStr"/>
+      <c r="S284" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="12" t="inlineStr">
@@ -21351,6 +22248,11 @@
       <c r="P285" s="8" t="inlineStr"/>
       <c r="Q285" s="8" t="inlineStr"/>
       <c r="R285" s="8" t="inlineStr"/>
+      <c r="S285" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="12" t="inlineStr">
@@ -21423,6 +22325,11 @@
       <c r="P286" s="8" t="inlineStr"/>
       <c r="Q286" s="8" t="inlineStr"/>
       <c r="R286" s="8" t="inlineStr"/>
+      <c r="S286" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="12" t="inlineStr">
@@ -21491,6 +22398,7 @@
       <c r="P287" s="15" t="inlineStr"/>
       <c r="Q287" s="15" t="inlineStr"/>
       <c r="R287" s="15" t="inlineStr"/>
+      <c r="S287" s="12" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="12" t="inlineStr">
@@ -21547,6 +22455,7 @@
       <c r="P288" s="15" t="inlineStr"/>
       <c r="Q288" s="15" t="inlineStr"/>
       <c r="R288" s="15" t="inlineStr"/>
+      <c r="S288" s="12" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="12" t="inlineStr">
@@ -21631,6 +22540,11 @@
         </is>
       </c>
       <c r="R289" s="8" t="inlineStr"/>
+      <c r="S289" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="12" t="inlineStr">
@@ -21711,6 +22625,11 @@
         </is>
       </c>
       <c r="R290" s="8" t="inlineStr"/>
+      <c r="S290" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="12" t="inlineStr">
@@ -21795,6 +22714,11 @@
         </is>
       </c>
       <c r="R291" s="8" t="inlineStr"/>
+      <c r="S291" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="12" t="inlineStr">
@@ -21879,6 +22803,11 @@
         </is>
       </c>
       <c r="R292" s="8" t="inlineStr"/>
+      <c r="S292" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="12" t="inlineStr">
@@ -21959,6 +22888,11 @@
         </is>
       </c>
       <c r="R293" s="8" t="inlineStr"/>
+      <c r="S293" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="12" t="inlineStr">
@@ -22027,6 +22961,7 @@
       <c r="P294" s="15" t="inlineStr"/>
       <c r="Q294" s="15" t="inlineStr"/>
       <c r="R294" s="15" t="inlineStr"/>
+      <c r="S294" s="12" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="12" t="inlineStr">
@@ -22083,6 +23018,7 @@
       <c r="P295" s="15" t="inlineStr"/>
       <c r="Q295" s="15" t="inlineStr"/>
       <c r="R295" s="15" t="inlineStr"/>
+      <c r="S295" s="12" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="12" t="inlineStr">
@@ -22163,6 +23099,11 @@
       </c>
       <c r="Q296" s="8" t="inlineStr"/>
       <c r="R296" s="8" t="inlineStr"/>
+      <c r="S296" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="12" t="inlineStr">
@@ -22243,6 +23184,11 @@
       </c>
       <c r="Q297" s="8" t="inlineStr"/>
       <c r="R297" s="8" t="inlineStr"/>
+      <c r="S297" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="12" t="inlineStr">
@@ -22323,6 +23269,11 @@
       </c>
       <c r="Q298" s="8" t="inlineStr"/>
       <c r="R298" s="8" t="inlineStr"/>
+      <c r="S298" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="12" t="inlineStr">
@@ -22399,6 +23350,11 @@
       </c>
       <c r="Q299" s="8" t="inlineStr"/>
       <c r="R299" s="8" t="inlineStr"/>
+      <c r="S299" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="12" t="inlineStr">
@@ -22475,6 +23431,11 @@
       <c r="P300" s="8" t="inlineStr"/>
       <c r="Q300" s="8" t="inlineStr"/>
       <c r="R300" s="8" t="inlineStr"/>
+      <c r="S300" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="12" t="inlineStr">
@@ -22547,10 +23508,15 @@
       <c r="P301" s="8" t="inlineStr"/>
       <c r="Q301" s="8" t="inlineStr"/>
       <c r="R301" s="8" t="inlineStr"/>
+      <c r="S301" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <autoFilter ref="A1:R301"/>
+  <autoFilter ref="A1:S301"/>
   <dataValidations count="1">
     <dataValidation sqref="O2:O301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Chỉ hai giá trị" error="verdict chỉ nhận: dat, khong_dat" type="list">
       <formula1>"dat,khong_dat"</formula1>

--- a/data/review/crosscheck_B.xlsx
+++ b/data/review/crosscheck_B.xlsx
@@ -746,7 +746,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>T6   Hết hiệu lực một phần ở cấp Khoản/Điểm. Cột đáp án ghi "(không có đáp án: ...)". Câu hỏi không được là dạng có/không. Nếu nội dung đã CHUYỂN CHỖ (đạt đủ 7 yếu tố, hướng dẫn §3) thì đáp án rỗng là sai: khong_dat, gold_wrong, ghi chỗ mới vào note. Không chắc thì vẫn dat (nếu không có lỗi khác) và ghi "unclear" vào note.</t>
+          <t>T6   Hết hiệu lực một phần ở cấp Khoản/Điểm. Cột đáp án ghi "(không có đáp án: ...)". Câu CHỈ hỏi có/không là group_mismatch; câu ghép có thêm vế hỏi nội dung ("... có áp dụng không, và quy định cụ thể thế nào?") thì chấm theo vế nội dung. Nếu nội dung đã CHUYỂN CHỖ (đạt đủ 7 yếu tố, hướng dẫn §3) thì đáp án rỗng là sai: khong_dat, gold_wrong, ghi chỗ mới vào note. Sáp nhập: cơ quan kế thừa (Bộ GTVT vào Bộ Xây dựng) đạt yếu tố 6; địa danh chỉ đổi tên do sáp nhập tỉnh/xã, phạm vi và ranh giới giữ nguyên (Bến Tre thành Vĩnh Long) đạt yếu tố 2. Không chắc thì vẫn dat (nếu không có lỗi khác) và ghi "unclear" vào note.</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Câu hỏi không làm được việc của nhóm. T2 không chạm chỗ thay đổi (hai mốc trả lời như nhau); T3 chỉ chạm một lần sửa; T6 hỏi kiểu có/không; T5 hỏi vào phần không đổi.</t>
+          <t>Câu hỏi không làm được việc của nhóm. T2 không chạm chỗ thay đổi (hai mốc trả lời như nhau); T3 chỉ chạm một lần sửa; T6 CHỈ hỏi có/không (câu ghép có thêm vế hỏi nội dung thì không tính); T5 hỏi vào phần không đổi.</t>
         </is>
       </c>
     </row>
